--- a/output/stock_quant_scores/JPM_balance_df.xlsx
+++ b/output/stock_quant_scores/JPM_balance_df.xlsx
@@ -1301,7 +1301,9 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
+      <c r="F6" t="n">
+        <v>354599000000</v>
+      </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
@@ -1309,16 +1311,22 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+      <c r="N6" t="n">
+        <v>294127000000</v>
+      </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
+      <c r="R6" t="n">
+        <v>272268000000</v>
+      </c>
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
+      <c r="W6" t="n">
+        <v>3449440000000</v>
+      </c>
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr"/>
@@ -1331,7 +1339,9 @@
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="inlineStr"/>
-      <c r="AH6" t="inlineStr"/>
+      <c r="AH6" t="n">
+        <v>3743567000000</v>
+      </c>
       <c r="AI6" t="inlineStr"/>
       <c r="AJ6" t="inlineStr"/>
       <c r="AK6" t="n">
@@ -1351,7 +1361,9 @@
       </c>
       <c r="AV6" t="inlineStr"/>
       <c r="AW6" t="inlineStr"/>
-      <c r="AX6" t="inlineStr"/>
+      <c r="AX6" t="n">
+        <v>740834000000</v>
+      </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr"/>
     </row>
